--- a/src/attributions/attributions_ig_traj_171.xlsx
+++ b/src/attributions/attributions_ig_traj_171.xlsx
@@ -999,61 +999,61 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.3938022143261778</v>
+        <v>-0.01009686677859327</v>
       </c>
       <c r="B2" t="n">
         <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04868411991929447</v>
+        <v>-0.09193307028727368</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.3050520701042835</v>
+        <v>-0.05579402086190505</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2690133259723669</v>
+        <v>-0.02584556243336364</v>
       </c>
       <c r="K2" t="n">
         <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05114917149819505</v>
+        <v>-0.08752701592675201</v>
       </c>
       <c r="O2" t="n">
         <v>-0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2259740445513439</v>
+        <v>-0.07472758820838235</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2296103360869784</v>
+        <v>0.002085890758407794</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -1065,22 +1065,22 @@
         <v>-0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1245000793392414</v>
+        <v>0.03731510124105564</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.09721794667373065</v>
+        <v>0.007375700342589841</v>
       </c>
       <c r="Z2" t="n">
         <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.09598937454672077</v>
+        <v>0.0717290325528676</v>
       </c>
       <c r="AC2" t="n">
         <v>-0</v>
@@ -1089,16 +1089,16 @@
         <v>-0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.07268199537749538</v>
+        <v>-0.03418842762287747</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.04767760583578441</v>
+        <v>-0.1021996763769829</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1107,91 +1107,91 @@
         <v>-0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.04519693265382037</v>
+        <v>0.002496250868223194</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.03864110750369897</v>
+        <v>0.01748142948273715</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.0978378742302646</v>
+        <v>-0.003344217266276548</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.3971574863018135</v>
+        <v>-0.04882178645402251</v>
       </c>
       <c r="AU2" t="n">
         <v>-0</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.07457676493489084</v>
+        <v>0.0578073764572434</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.1586782494568163</v>
+        <v>-0.04535874214771602</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.1800111163786079</v>
+        <v>0.06993203385595755</v>
       </c>
       <c r="BD2" t="n">
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.05512854432142648</v>
+        <v>-0.1538617367130594</v>
       </c>
       <c r="BH2" t="n">
         <v>-0</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0.2476265283158801</v>
+        <v>-0.02788424497407228</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.07686050923880729</v>
+        <v>-0.0180427526364786</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN2" t="n">
         <v>-0</v>
@@ -1200,49 +1200,49 @@
         <v>-0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.08029671892190467</v>
+        <v>0.04108384765882749</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.004535525175122443</v>
+        <v>0.006613364376083035</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
         <v>-0</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.1389908877275317</v>
+        <v>-0.01943040455043475</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
         <v>-0</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.01807240370399503</v>
+        <v>-0.01362663485799079</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0.06561732365814493</v>
+        <v>-0.0007174785524422969</v>
       </c>
       <c r="CB2" t="n">
         <v>-0</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0.121212647800344</v>
+        <v>-0.000491159435906297</v>
       </c>
       <c r="CE2" t="n">
         <v>0</v>
@@ -1251,43 +1251,43 @@
         <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.02849564958752479</v>
+        <v>0.05462401719442944</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.1438264160316918</v>
+        <v>0.0137636340855169</v>
       </c>
       <c r="CK2" t="n">
         <v>-0</v>
       </c>
       <c r="CL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0.06021880792591472</v>
+        <v>-0.03675678482136786</v>
       </c>
       <c r="CN2" t="n">
         <v>0</v>
       </c>
       <c r="CO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.09760165580647215</v>
+        <v>-0.002900004187523966</v>
       </c>
       <c r="CR2" t="n">
         <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.1032967514534912</v>
+        <v>0.0207182913375436</v>
       </c>
       <c r="CT2" t="n">
         <v>-0</v>
@@ -1296,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0.09247055509656449</v>
+        <v>0.006107647692540787</v>
       </c>
       <c r="CW2" t="n">
         <v>-0</v>
@@ -1308,22 +1308,22 @@
         <v>0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.007590221591635965</v>
+        <v>0.03216990683364031</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.1371440541260591</v>
+        <v>0.01980849143728176</v>
       </c>
       <c r="DC2" t="n">
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0.03511313511746859</v>
+        <v>0.007388230253724388</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1335,40 +1335,40 @@
         <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.002197943831781576</v>
+        <v>-0.0003222481326404165</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.05666330533067102</v>
+        <v>0.02682732203358859</v>
       </c>
       <c r="DL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN2" t="n">
-        <v>-0.07819614177297413</v>
+        <v>-0.02716996208182842</v>
       </c>
       <c r="DO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DP2" t="n">
         <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.1258896115902789</v>
+        <v>-0.0522619084851141</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.1017136790890469</v>
+        <v>0.03375066827003824</v>
       </c>
       <c r="DU2" t="n">
         <v>-0</v>
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0.09222924948158027</v>
+        <v>0.03859117312273033</v>
       </c>
       <c r="DX2" t="n">
         <v>0</v>
@@ -1389,13 +1389,13 @@
         <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.1192997935037226</v>
+        <v>-0.03585671805649304</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.1501365509168263</v>
+        <v>-0.01450082330229197</v>
       </c>
       <c r="ED2" t="n">
         <v>0</v>
@@ -1404,34 +1404,34 @@
         <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0.1185445022089335</v>
+        <v>0.02561800604323034</v>
       </c>
       <c r="EG2" t="n">
         <v>0</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.1461507086311469</v>
+        <v>0.07638196954943562</v>
       </c>
       <c r="EK2" t="n">
         <v>0</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.01636510873211273</v>
+        <v>0.02408654362906813</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>-0.0956002320284447</v>
+        <v>0.06643814091090311</v>
       </c>
       <c r="EP2" t="n">
         <v>0</v>
@@ -1443,49 +1443,49 @@
         <v>-0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.1587497387724906</v>
+        <v>-0.05265028648807039</v>
       </c>
       <c r="ET2" t="n">
         <v>-0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0.04383919451510769</v>
+        <v>0.0042452147723991</v>
       </c>
       <c r="EV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX2" t="n">
-        <v>-0.08744727400540719</v>
+        <v>0.007869395356711134</v>
       </c>
       <c r="EY2" t="n">
         <v>0</v>
       </c>
       <c r="EZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA2" t="n">
         <v>-0</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.02915083972522742</v>
+        <v>0.02077219982335493</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.126553351680475</v>
+        <v>0.01518043619224797</v>
       </c>
       <c r="FE2" t="n">
         <v>-0</v>
       </c>
       <c r="FF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.03105626285079227</v>
+        <v>0.06093256090139129</v>
       </c>
       <c r="FH2" t="n">
         <v>0</v>
@@ -1497,40 +1497,40 @@
         <v>0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.05796907862176165</v>
+        <v>0.08962149109789183</v>
       </c>
       <c r="FL2" t="n">
         <v>0</v>
       </c>
       <c r="FM2" t="n">
-        <v>-0.1401273990284627</v>
+        <v>-0.006774211414735051</v>
       </c>
       <c r="FN2" t="n">
         <v>-0</v>
       </c>
       <c r="FO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0.05432549592034229</v>
+        <v>-0.006411793917361764</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR2" t="n">
         <v>0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.1591113889600599</v>
+        <v>-0.1160410899274398</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.1105658327332261</v>
+        <v>0.1970426683518036</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
@@ -1539,7 +1539,7 @@
         <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.02057975559658688</v>
+        <v>0.03761997345061538</v>
       </c>
       <c r="FZ2" t="n">
         <v>-0</v>
@@ -1548,7 +1548,7 @@
         <v>-0</v>
       </c>
       <c r="GB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC2" t="n">
         <v>0</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>-0.09944329364667712</v>
+        <v>0.003960505044904639</v>
       </c>
       <c r="GF2" t="n">
         <v>0</v>
@@ -1568,37 +1568,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.2894843396322407</v>
+        <v>-0.1354638205401537</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006580024302947555</v>
+        <v>-0.05379159647318964</v>
       </c>
       <c r="F3" t="n">
-        <v>0.704293921453623</v>
+        <v>0.2632836239191449</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1608686701784171</v>
+        <v>-0.1253217635757364</v>
       </c>
       <c r="L3" t="n">
         <v>-0</v>
@@ -1607,52 +1607,52 @@
         <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.02370372674238558</v>
+        <v>0.01588264937778133</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5904326017846143</v>
+        <v>0.2524490050065897</v>
       </c>
       <c r="P3" t="n">
         <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.02513059754099996</v>
+        <v>-0.1216125452661049</v>
       </c>
       <c r="U3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.07563394814976175</v>
+        <v>0.02026937236568369</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1266969136384135</v>
+        <v>0.0527928942456429</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.2062835709664396</v>
+        <v>0.03798640032241681</v>
       </c>
       <c r="AD3" t="n">
         <v>-0</v>
@@ -1661,43 +1661,43 @@
         <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.002773127849136634</v>
+        <v>0.09587988013956497</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.06300508280077848</v>
+        <v>0.08161032300366643</v>
       </c>
       <c r="AH3" t="n">
         <v>-0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.09159870301380431</v>
+        <v>-0.08314547379909779</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.1994180907135524</v>
+        <v>-0.1047361770407622</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.2107628036890458</v>
+        <v>0.1385407267628224</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
         <v>-0</v>
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.3724360538563026</v>
+        <v>-0.3691699452976587</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1715,25 +1715,25 @@
         <v>-0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1253263858627205</v>
+        <v>-0.1171507015482715</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.741375679814274</v>
+        <v>0.3852494369570571</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.1177606760966242</v>
+        <v>0.1595728219284575</v>
       </c>
       <c r="BE3" t="n">
         <v>-0</v>
@@ -1742,25 +1742,25 @@
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.1095284455060586</v>
+        <v>0.1746433843191853</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.02145688132860294</v>
+        <v>0.008151516938672682</v>
       </c>
       <c r="BI3" t="n">
         <v>-0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.1393056225404845</v>
+        <v>0.00835156489534615</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
@@ -1769,37 +1769,37 @@
         <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.06192919826469847</v>
+        <v>-0.04271834274944846</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.05875995075331611</v>
+        <v>0.01618749708665215</v>
       </c>
       <c r="BR3" t="n">
         <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.07812139223712557</v>
+        <v>-0.08491540353493002</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
         <v>-0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.09131781014201998</v>
+        <v>-0.03457823953367689</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.2338964749073431</v>
+        <v>0.1426007601937536</v>
       </c>
       <c r="CA3" t="n">
         <v>0</v>
@@ -1814,34 +1814,34 @@
         <v>-0</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.1359111806249459</v>
+        <v>0.1151832147454432</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.002821803880350757</v>
+        <v>0.03051216147802744</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.147747936360737</v>
+        <v>-0.125380678480225</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
         <v>-0</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.00573229374159587</v>
+        <v>0.04180091602003818</v>
       </c>
       <c r="CO3" t="n">
         <v>0</v>
@@ -1850,16 +1850,16 @@
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.1559309909679938</v>
+        <v>-0.07132205046036356</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.05030099512793456</v>
+        <v>-0.1925186403808381</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
         <v>0</v>
@@ -1868,142 +1868,142 @@
         <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.1081971623401299</v>
+        <v>0.1183414934700485</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.003328394640530784</v>
+        <v>0.01378139373590568</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0.1867182911613391</v>
+        <v>-0.1220926081286807</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD3" t="n">
         <v>-0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.03172402534234121</v>
+        <v>-0.004258224249473345</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.008418701884115587</v>
+        <v>0.009031781602589812</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.04088772470950795</v>
+        <v>-0.05301063784102028</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL3" t="n">
         <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
         <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.005395591247767693</v>
+        <v>0.02997755857969522</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ3" t="n">
         <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.03287856468360251</v>
+        <v>0.001756428198014009</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.06564826704492548</v>
+        <v>-0.103681849540317</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV3" t="n">
         <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.09633524897025886</v>
+        <v>0.02161108857720348</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
         <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.05124235679224277</v>
+        <v>0.005277575753897486</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.1201960475642312</v>
+        <v>-0.03246859377154758</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED3" t="n">
         <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
         <v>-0</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.05764070960305256</v>
+        <v>0.07265602893140141</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI3" t="n">
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.1085285629109779</v>
+        <v>0.02956036001060944</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.1055066321527088</v>
+        <v>0.0006132346931263081</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
       </c>
       <c r="EM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN3" t="n">
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.09734299224101295</v>
+        <v>-0.0733808868454439</v>
       </c>
       <c r="EQ3" t="n">
         <v>0</v>
@@ -2012,16 +2012,16 @@
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.06285004637983321</v>
+        <v>-0.08889328739354481</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.07581983674180601</v>
+        <v>-0.01996338507594583</v>
       </c>
       <c r="EU3" t="n">
         <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
         <v>0</v>
@@ -2030,46 +2030,46 @@
         <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.0974684485810203</v>
+        <v>0.1254158468590597</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA3" t="n">
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.008364770262872174</v>
+        <v>0.03946135964079589</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0.1520082243709805</v>
+        <v>-0.1202285083697304</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
         <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.03723938255965383</v>
+        <v>0.1047751946025173</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.02777524466975322</v>
+        <v>0.002995997007051451</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.1462352520229984</v>
+        <v>0.1537567570310592</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
@@ -2081,10 +2081,10 @@
         <v>-0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.1022636598140699</v>
+        <v>0.2064920505826041</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
@@ -2093,54 +2093,54 @@
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.19814909065548</v>
+        <v>0.005438591853113925</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.06214063412688727</v>
+        <v>0.07506576457206433</v>
       </c>
       <c r="FV3" t="n">
         <v>0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.01992160324238639</v>
+        <v>0.07423651575042176</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.09975216806945505</v>
+        <v>-0.002274519158858946</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2755258249281843</v>
+        <v>0.405020222265589</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2149,10 +2149,10 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.06492836816048551</v>
+        <v>0.06372926250152276</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.204497133225938</v>
+        <v>-0.4251100896151447</v>
       </c>
       <c r="G4" t="n">
         <v>-0</v>
@@ -2161,13 +2161,13 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2394854609441788</v>
+        <v>0.4317521272632124</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,64 +2176,64 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.00970790053260227</v>
+        <v>-0.1198726529183301</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1432068252116536</v>
+        <v>-0.3997806439462324</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02571055178553928</v>
+        <v>0.1281639823399459</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.04328334879629617</v>
+        <v>-0.05703276540578284</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002470851453459564</v>
+        <v>-0.1037767909528199</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.01158050473226523</v>
+        <v>-0.1095799857789832</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.001070190356738853</v>
+        <v>-0.2468683596267923</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.03081253672139382</v>
+        <v>0.1103358290962077</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -2248,19 +2248,19 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.03161417360884488</v>
+        <v>0.1310487906846777</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.0183896328089442</v>
+        <v>-0.02074229970055991</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.06362833186277897</v>
+        <v>-0.1026254462108533</v>
       </c>
       <c r="AQ4" t="n">
         <v>-0</v>
@@ -2272,37 +2272,37 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.2061149687676839</v>
+        <v>0.5732363015967256</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.05133443669933167</v>
+        <v>-0.3068647865287035</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.1431815344385163</v>
+        <v>-0.417826589388127</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.07525200905589015</v>
+        <v>-0.07260255830645147</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,25 +2311,25 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.05893207595619136</v>
+        <v>0.06339971310477943</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.08903067774101013</v>
+        <v>-0.07013979051847419</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ4" t="n">
         <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.06008887002168575</v>
+        <v>0.08911388918297611</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
@@ -2338,25 +2338,25 @@
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.02767248257505334</v>
+        <v>0.04057829006772086</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01948861954788203</v>
+        <v>0.08548936850812554</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.0725249700044187</v>
+        <v>0.1968008826689391</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,37 +2365,37 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.01917982713248319</v>
+        <v>-0.02665386706205927</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.02567385600338756</v>
+        <v>-0.1309997434669045</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
         <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.05646449051392896</v>
+        <v>-0.1548475551947182</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
         <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.003965315100631192</v>
+        <v>0.03987324885462569</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.05767913336282289</v>
+        <v>0.138204725059459</v>
       </c>
       <c r="CJ4" t="n">
         <v>-0</v>
@@ -2410,46 +2410,46 @@
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.002615165114181482</v>
+        <v>-0.1327519335459714</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.001456018823493317</v>
+        <v>0.1928771426723679</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.0437817946841828</v>
+        <v>-0.01963679564291157</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
         <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.05101108946540956</v>
+        <v>-0.1527453425625379</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
         <v>0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.002304887530023189</v>
+        <v>0.0346123183211647</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.06143717171175294</v>
+        <v>0.1731155248870737</v>
       </c>
       <c r="DB4" t="n">
         <v>0</v>
@@ -2458,40 +2458,40 @@
         <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.007061867433795261</v>
+        <v>0.02708209637042656</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0811188553538793</v>
+        <v>-0.07061649321783686</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.845195236035354e-05</v>
+        <v>0.05100448248911048</v>
       </c>
       <c r="DK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.02867783031109391</v>
+        <v>-0.1229682322830714</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
@@ -2500,16 +2500,16 @@
         <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.01433278288697825</v>
+        <v>0.002414312099513621</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.01105013427159111</v>
+        <v>0.1647295397777635</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
@@ -2518,46 +2518,46 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.05137517834268427</v>
+        <v>-0.02048394194962008</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
         <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.02718044773268719</v>
+        <v>0.06656946150919971</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.03947245291474771</v>
+        <v>0.07739911502049111</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.05248015543422756</v>
+        <v>-0.06439102698223909</v>
       </c>
       <c r="EH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI4" t="n">
         <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.01539468396701377</v>
+        <v>-0.02870277182391009</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.06455462074961942</v>
+        <v>0.03985231897036959</v>
       </c>
       <c r="EL4" t="n">
         <v>-0</v>
@@ -2566,13 +2566,13 @@
         <v>-0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.03434589067990546</v>
+        <v>-0.07513553425988762</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
@@ -2581,13 +2581,13 @@
         <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.01263472047024843</v>
+        <v>-0.105349038891563</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0.01302188632892642</v>
+        <v>0.0087581709705711</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
@@ -2599,61 +2599,61 @@
         <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.04944928083076845</v>
+        <v>-0.1703418725999054</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
         <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.00466098849454194</v>
+        <v>0.009225280432878194</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.05740051153665914</v>
+        <v>0.1538711331049554</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.01390280895665056</v>
+        <v>0.1449232269162577</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.005721239776736639</v>
+        <v>-0.07478144136033103</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.03089961845139688</v>
+        <v>0.1793862669391168</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO4" t="n">
         <v>0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.004318561172450252</v>
+        <v>0.06161370376982636</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
@@ -2662,37 +2662,37 @@
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.02830880490512632</v>
+        <v>-0.07613790300248933</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.03562895596549798</v>
+        <v>-0.02554206156088053</v>
       </c>
       <c r="FV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.0009116652555951593</v>
+        <v>-0.04589258961790669</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.0119843347930833</v>
+        <v>0.2223288923140189</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
@@ -2701,7 +2701,7 @@
         <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,73 +2709,73 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3694532871327955</v>
+        <v>0.2364146927472041</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1201493077321622</v>
+        <v>-0.09837540476265959</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.106078842256138</v>
+        <v>0.02851122526489636</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.06317956264779863</v>
+        <v>-0.06387116679465267</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.301358449371957</v>
+        <v>0.254184366338777</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.07613095210577185</v>
+        <v>-0.1224331013470458</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.05791112078894675</v>
+        <v>-0.03197710576783411</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.06611399102013746</v>
+        <v>-0.05162251531902547</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.07079111034847746</v>
+        <v>0.08401946622941955</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.02017491081063709</v>
+        <v>-0.04217034143666364</v>
       </c>
       <c r="W5" t="n">
-        <v>0.08124882569074741</v>
+        <v>-0.07806677351703899</v>
       </c>
       <c r="X5" t="n">
-        <v>0.006748867212271283</v>
+        <v>-0.06139117091868761</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
@@ -2787,130 +2787,130 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.04886617283242344</v>
+        <v>-0.08685651743526977</v>
       </c>
       <c r="AD5" t="n">
         <v>-0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.01998521909183749</v>
+        <v>-0.09928873311900148</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.02584883717397595</v>
+        <v>-0.06423473805694452</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.01934232954904554</v>
+        <v>0.05253266170165188</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01425278365764937</v>
+        <v>0.05456446555349607</v>
       </c>
       <c r="AM5" t="n">
         <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.05885032735386687</v>
+        <v>-0.05401016610294541</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.0596792208175272</v>
+        <v>0.05293413071124901</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.03734451094494778</v>
+        <v>-0.04178089429491233</v>
       </c>
       <c r="AQ5" t="n">
         <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3238331730917484</v>
+        <v>0.2589582496575185</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.04324848198620739</v>
+        <v>-0.03865904802062076</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.02937239900335384</v>
+        <v>-0.08495768189844166</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.04375711516681704</v>
+        <v>-0.1012780541015261</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
         <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.05167348632288866</v>
+        <v>-0.01770658421516293</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.07955093118622197</v>
+        <v>-0.08935826977796767</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1116914058386765</v>
+        <v>-0.05136052699201238</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.08414606449034499</v>
+        <v>-0.02943070881785713</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.08000416037114691</v>
+        <v>-0.03369542269308888</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.05586068237683024</v>
+        <v>0.0599254880853754</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1194637593794258</v>
+        <v>0.03266745860365652</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.03031989054633144</v>
+        <v>-0.01004145317464008</v>
       </c>
       <c r="BR5" t="n">
         <v>0</v>
@@ -2919,31 +2919,31 @@
         <v>-0</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.08673212658926806</v>
+        <v>0.1030469887164834</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.004593398800621502</v>
+        <v>-0.02348014960754849</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0112214419673465</v>
+        <v>0.01280975867306597</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.006185778035645527</v>
+        <v>-0.0512139128121379</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>-0</v>
@@ -2952,25 +2952,25 @@
         <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.07796029241944803</v>
+        <v>-0.07789571400717461</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.004703188963560567</v>
+        <v>0.06550721315157947</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.0003753740793287614</v>
+        <v>-0.00869242503377236</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.03129531144653609</v>
+        <v>0.0163940789725587</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL5" t="n">
         <v>0</v>
@@ -2979,52 +2979,52 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.003379435663676963</v>
+        <v>-0.03263598111338146</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.06312649354337084</v>
+        <v>0.1291507341554377</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.08108015070047044</v>
+        <v>0.05552105185600111</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.05087378597665723</v>
+        <v>0.04621832899427842</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.059855303919773</v>
+        <v>-0.07626805400467351</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.03183717778404103</v>
+        <v>0.06971559885572035</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.002623548317212002</v>
+        <v>0.002591181498692777</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.03268192620317573</v>
+        <v>0.02576436495008021</v>
       </c>
       <c r="DB5" t="n">
         <v>0</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD5" t="n">
         <v>-0</v>
@@ -3033,19 +3033,19 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.0150351806050066</v>
+        <v>-0.03116490280688861</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0564800070019654</v>
+        <v>0.009430095180138534</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.005448230357230063</v>
+        <v>0.01216448602918218</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.02160291818655201</v>
+        <v>0.02508927375329784</v>
       </c>
       <c r="DK5" t="n">
         <v>-0</v>
@@ -3054,25 +3054,25 @@
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.0128089280286045</v>
+        <v>-0.01073319957144691</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.06238227727532547</v>
+        <v>0.009511293617483534</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.02187132213573931</v>
+        <v>-0.0617665500131073</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.02726149558088034</v>
+        <v>0.01667140986909774</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
@@ -3084,76 +3084,76 @@
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.04829024479286884</v>
+        <v>-0.008228068708022567</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.0241358802354509</v>
+        <v>0.07063915115054735</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0342973578962124</v>
+        <v>-0.002605545486912772</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.05845071095831052</v>
+        <v>0.004331529449029596</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.08772061378131157</v>
+        <v>-0.06236104616112521</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.03882054561856284</v>
+        <v>0.05119716491637583</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.06614520598718032</v>
+        <v>0.03604327099915579</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.02208907225157403</v>
+        <v>-0.04267069066468405</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>-0</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.03981605130173743</v>
+        <v>-0.02639969140344399</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.007158178357422127</v>
+        <v>0.0430085845233904</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.02468534606957337</v>
+        <v>-0.01755936430917555</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.03358515721009882</v>
+        <v>0.03755110331030392</v>
       </c>
       <c r="EU5" t="n">
         <v>0</v>
@@ -3168,19 +3168,19 @@
         <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.06065417263721548</v>
+        <v>-0.08006886639634073</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.004564047750212546</v>
+        <v>0.08965074870474331</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.01401243305891759</v>
+        <v>-0.02324592613762326</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.03741622161092956</v>
+        <v>0.02148876749303454</v>
       </c>
       <c r="FD5" t="n">
         <v>0</v>
@@ -3195,22 +3195,22 @@
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.02967019244927751</v>
+        <v>0.0980303005363611</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.05619489250679095</v>
+        <v>0.05368462444065113</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.01414901746846079</v>
+        <v>0.01392432313397117</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0.008732920427275265</v>
+        <v>0.07589248088999746</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN5" t="n">
         <v>-0</v>
@@ -3219,52 +3219,52 @@
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.004005238507743286</v>
+        <v>0.009737843138777947</v>
       </c>
       <c r="FR5" t="n">
         <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.01703143380890867</v>
+        <v>0.1013308913174651</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.03725680590032083</v>
+        <v>-0.02508659213508916</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.03919955839753179</v>
+        <v>-0.03045687956525964</v>
       </c>
       <c r="FV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.04031895800977078</v>
+        <v>-0.06806121882885464</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.07569762397205471</v>
+        <v>0.03286297300467071</v>
       </c>
       <c r="GC5" t="n">
         <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0.04165466825632142</v>
+        <v>0.04816472334260115</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF5" t="n">
         <v>0</v>
@@ -3278,49 +3278,49 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.3438116639870767</v>
+        <v>0.2318319737746851</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.06668499094194343</v>
+        <v>-0.1055342469314975</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0364752059208738</v>
+        <v>-0.01826382788248208</v>
       </c>
       <c r="F6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2323967045121962</v>
+        <v>0.2763805201083936</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.09179077263011975</v>
+        <v>-0.1282710006845446</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.04690605313107066</v>
+        <v>-0.04838170570842442</v>
       </c>
       <c r="O6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3332,70 +3332,70 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.08384865396667288</v>
+        <v>0.03489870195414244</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.04808717573136204</v>
+        <v>-0.02955779122174678</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1302540369275459</v>
+        <v>-0.03447426939228827</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1021263351355602</v>
+        <v>-0.04546890398287862</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.002319977227769498</v>
+        <v>-0.08307840441950014</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.05504551930785918</v>
+        <v>-0.05270080153236473</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0440260401992733</v>
+        <v>0.06569261949474377</v>
       </c>
       <c r="AM6" t="n">
         <v>-0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.05345836035298392</v>
+        <v>-0.06676239146808574</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.02217558500385006</v>
+        <v>0.04631976780846992</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
@@ -3404,61 +3404,61 @@
         <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.3183908640638838</v>
+        <v>0.2020124348634385</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.1359442842659188</v>
+        <v>-0.06150445624175509</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.1518271900009334</v>
+        <v>-0.09734708410111427</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.02185101578438996</v>
+        <v>0.002414354013821389</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.1623377606079976</v>
+        <v>-0.03214516521234582</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.1230685023028073</v>
+        <v>-0.02160564728555752</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
@@ -3467,19 +3467,19 @@
         <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.07898677758722253</v>
+        <v>-0.01120924440666267</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.007315093255475858</v>
+        <v>0.02818316512118992</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.1919122380428723</v>
+        <v>0.04673940525191485</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
         <v>0</v>
@@ -3488,52 +3488,52 @@
         <v>-0</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.09011057133532482</v>
+        <v>0.0829281413352994</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.0357838536480021</v>
+        <v>-0.02705555456839545</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.06454587293008848</v>
+        <v>-0.002999897531873651</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.08206121575279821</v>
+        <v>-0.0733646452156498</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.0203963756565792</v>
+        <v>0.06159618501766827</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.006300761843916369</v>
+        <v>-0.0009103893594305519</v>
       </c>
       <c r="CI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
@@ -3542,28 +3542,28 @@
         <v>0</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.02187097891290269</v>
+        <v>-0.06205662152109965</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.1317712049625057</v>
+        <v>0.1295158182323</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.1063684947281441</v>
+        <v>0.02147557524763602</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT6" t="n">
         <v>0</v>
@@ -3572,46 +3572,46 @@
         <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.05614421835079308</v>
+        <v>-0.07117176142385044</v>
       </c>
       <c r="CX6" t="n">
         <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.0006052411601386537</v>
+        <v>0.06560921014392193</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.01317283812819755</v>
+        <v>0.005913490920410524</v>
       </c>
       <c r="DA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.04278183918028314</v>
+        <v>-0.03913399489548414</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.03334621375761366</v>
+        <v>0.03238580998184849</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.02206517767788532</v>
+        <v>-0.03447324244154491</v>
       </c>
       <c r="DJ6" t="n">
         <v>-0</v>
@@ -3629,19 +3629,19 @@
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.05080086482455457</v>
+        <v>-0.03439240062418648</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.04777858819569205</v>
+        <v>-0.01607710996810241</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.04271040790145936</v>
+        <v>-0.02112949349694825</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
@@ -3650,76 +3650,76 @@
         <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW6" t="n">
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.02947476765106043</v>
+        <v>-0.007801919706635443</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.03289909360897093</v>
+        <v>0.0628476793267192</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.009759899830155542</v>
+        <v>-0.02512874572365525</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.07423666022869602</v>
+        <v>-0.05409224841650533</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.009668036159286261</v>
+        <v>0.03876122441688517</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.08872154828900254</v>
+        <v>0.04076131206668748</v>
       </c>
       <c r="EK6" t="n">
         <v>0</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
         <v>0</v>
       </c>
       <c r="EN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.02431342131128654</v>
+        <v>-0.02536020060621257</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.0211258344564127</v>
+        <v>0.03321822580961781</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.02315041085613775</v>
+        <v>-0.01566186482625262</v>
       </c>
       <c r="ET6" t="n">
         <v>0</v>
@@ -3731,49 +3731,49 @@
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.05731144194823702</v>
+        <v>-0.07885366847354572</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>-0.03122942534572026</v>
+        <v>0.07870547335953963</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.006817645584025781</v>
+        <v>-0.008728431344551394</v>
       </c>
       <c r="FC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD6" t="n">
         <v>0</v>
       </c>
       <c r="FE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG6" t="n">
         <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.008675601325849625</v>
+        <v>0.07779627601608774</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.001945876880924079</v>
+        <v>0.04703506880186738</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.02869794252845428</v>
+        <v>-0.007633789709656887</v>
       </c>
       <c r="FL6" t="n">
         <v>-0</v>
@@ -3785,25 +3785,25 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.002210654611916264</v>
+        <v>0.001937685013807634</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.02217272212118767</v>
+        <v>0.07149436428610489</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.004905419685142409</v>
+        <v>-0.009594951381279391</v>
       </c>
       <c r="FU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV6" t="n">
         <v>0</v>
@@ -3815,39 +3815,39 @@
         <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.01287889391507899</v>
+        <v>-0.05193053893176117</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>-0.1154313790071256</v>
+        <v>0.0179541372701983</v>
       </c>
       <c r="GC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.3315543892809102</v>
+        <v>-0.165568207106956</v>
       </c>
       <c r="C7" t="n">
         <v>-0</v>
@@ -3856,25 +3856,25 @@
         <v>-0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07666755896090115</v>
+        <v>0.07884927677811288</v>
       </c>
       <c r="F7" t="n">
-        <v>1.033044029201602</v>
+        <v>0.3127735476485545</v>
       </c>
       <c r="G7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2935583711115533</v>
+        <v>-0.2198368725511436</v>
       </c>
       <c r="L7" t="n">
         <v>-0</v>
@@ -3883,13 +3883,13 @@
         <v>-0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.07009031831491096</v>
+        <v>0.1515340633234578</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8574417820790873</v>
+        <v>0.4114495195932215</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -3898,10 +3898,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.005335767159138302</v>
+        <v>-0.1071091432611775</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,10 +3910,10 @@
         <v>-0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1604568618313796</v>
+        <v>0.05877261611779534</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1492988004105616</v>
+        <v>0.08366313484153308</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -3925,91 +3925,91 @@
         <v>-0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.01367738674115263</v>
+        <v>0.02512261364540485</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.04846916225135422</v>
+        <v>0.1616423925520302</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.03838207396274902</v>
+        <v>-0.006248983035295521</v>
       </c>
       <c r="AH7" t="n">
         <v>-0</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK7" t="n">
         <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.03474040686563112</v>
+        <v>-0.06091622371524009</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.0224477170635593</v>
+        <v>0.01742784635275039</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.1700032004544386</v>
+        <v>0.08255684735471984</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
         <v>-0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.2221876145571115</v>
+        <v>-0.2650127663948265</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW7" t="n">
         <v>-0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.2734928770113581</v>
+        <v>0.1366306246068647</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.7825007548973365</v>
+        <v>0.2348793137059716</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
         <v>-0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.1171302075292977</v>
+        <v>0.1359001061410542</v>
       </c>
       <c r="BE7" t="n">
         <v>-0</v>
@@ -4018,10 +4018,10 @@
         <v>-0</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.05348463471216348</v>
+        <v>0.05232032298091423</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.1865724259514154</v>
+        <v>-0.002928266459616007</v>
       </c>
       <c r="BI7" t="n">
         <v>-0</v>
@@ -4030,40 +4030,40 @@
         <v>0</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.1720882433597597</v>
+        <v>-0.0847904736559095</v>
       </c>
       <c r="BN7" t="n">
         <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.05748596741152587</v>
+        <v>-0.07067643589905147</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.08571816072910454</v>
+        <v>-0.03315452830631724</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
         <v>-0</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.1087602545934374</v>
+        <v>-0.1320806896664829</v>
       </c>
       <c r="BW7" t="n">
         <v>-0</v>
@@ -4072,10 +4072,10 @@
         <v>-0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.09823411546148268</v>
+        <v>0.01472617522666507</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.2721891536069246</v>
+        <v>0.1310315472618229</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
@@ -4090,34 +4090,34 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.07861483346028969</v>
+        <v>0.07407259607048379</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.05135513785207683</v>
+        <v>-0.04641885809491544</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.2043129677907541</v>
+        <v>-0.07448456780050969</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK7" t="n">
         <v>-0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>-0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.0514453918371791</v>
+        <v>0.05723610841634751</v>
       </c>
       <c r="CO7" t="n">
         <v>0</v>
@@ -4126,16 +4126,16 @@
         <v>0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.2593940484279468</v>
+        <v>-0.1099368965743418</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.03063390755282392</v>
+        <v>-0.01557560789063341</v>
       </c>
       <c r="CS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU7" t="n">
         <v>0</v>
@@ -4144,61 +4144,61 @@
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.05908299028522825</v>
+        <v>0.06964424193540865</v>
       </c>
       <c r="CX7" t="n">
         <v>-0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.03623008007098741</v>
+        <v>-0.05935632571522591</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0.2062664070779253</v>
+        <v>-0.09917386776563673</v>
       </c>
       <c r="DB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC7" t="n">
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
         <v>-0</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.04141135020070766</v>
+        <v>0.0971357913697226</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.0905901842875516</v>
+        <v>0.04183536614768178</v>
       </c>
       <c r="DJ7" t="n">
-        <v>-0.07402491111291939</v>
+        <v>-0.0502169546412565</v>
       </c>
       <c r="DK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL7" t="n">
         <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.02820244492951384</v>
+        <v>-0.03307262464890974</v>
       </c>
       <c r="DP7" t="n">
         <v>-0</v>
@@ -4207,13 +4207,13 @@
         <v>-0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.1019373597298211</v>
+        <v>0.05958142805787685</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0.08235226720640965</v>
+        <v>-0.08903085906318707</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
@@ -4225,19 +4225,19 @@
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.08015565888284445</v>
+        <v>0.09012448454440626</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.05666788756798959</v>
+        <v>-0.01181821311779927</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.1225630172305461</v>
+        <v>0.002936186132100436</v>
       </c>
       <c r="EC7" t="n">
         <v>0</v>
@@ -4246,106 +4246,106 @@
         <v>-0</v>
       </c>
       <c r="EE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF7" t="n">
         <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.05561377214507678</v>
+        <v>0.05353277958034066</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.02504866241739046</v>
+        <v>-0.05198449150644427</v>
       </c>
       <c r="EK7" t="n">
-        <v>-0.1211240756501744</v>
+        <v>0.01481817184556554</v>
       </c>
       <c r="EL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO7" t="n">
         <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.01483852739103692</v>
+        <v>0.05900344545523646</v>
       </c>
       <c r="EQ7" t="n">
         <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.0317136911513799</v>
+        <v>-0.04857452648898018</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0.01109326151239741</v>
+        <v>0.04591305952067022</v>
       </c>
       <c r="EU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV7" t="n">
         <v>-0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.0369122329486032</v>
+        <v>0.08804228160475704</v>
       </c>
       <c r="EZ7" t="n">
         <v>0</v>
       </c>
       <c r="FA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.0647371640167072</v>
+        <v>-0.02829515694872746</v>
       </c>
       <c r="FC7" t="n">
-        <v>-0.1767849880194736</v>
+        <v>-0.08948781536527958</v>
       </c>
       <c r="FD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE7" t="n">
         <v>-0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
         <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.04842237741095196</v>
+        <v>-0.04496413381023746</v>
       </c>
       <c r="FI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ7" t="n">
         <v>0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.01737408666937787</v>
+        <v>0.01908697535428941</v>
       </c>
       <c r="FL7" t="n">
-        <v>-0.1552452505490127</v>
+        <v>-0.1170274361714624</v>
       </c>
       <c r="FM7" t="n">
         <v>-0</v>
@@ -4360,55 +4360,55 @@
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.005672900845261564</v>
+        <v>-0.00247690984737604</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
         <v>0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.008225056864448643</v>
+        <v>0.009605553181029439</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0.2052803311436839</v>
+        <v>0.09771176450418144</v>
       </c>
       <c r="FV7" t="n">
         <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
         <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.06256832481173993</v>
+        <v>0.05717110816535274</v>
       </c>
       <c r="GA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.00233280559055606</v>
+        <v>-0.07661384210471374</v>
       </c>
       <c r="GE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF7" t="n">
         <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4416,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.666877792282639</v>
+        <v>0.9154176255340356</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -4425,25 +4425,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01734619152356717</v>
+        <v>-0.2952771180719096</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.832647884736646</v>
+        <v>-0.8210146960521149</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5830538301467535</v>
+        <v>1.161822300127267</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03681076055061933</v>
+        <v>-0.9796835448708368</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6807683665932025</v>
+        <v>-0.9466126626393371</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q8" t="n">
         <v>-0</v>
@@ -4467,10 +4467,10 @@
         <v>-0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05347593031280914</v>
+        <v>0.2769772541037757</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -4479,43 +4479,43 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.05489386199670537</v>
+        <v>-0.1634675324324047</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1131082735367728</v>
+        <v>-0.1530207755476072</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.1221656106063273</v>
+        <v>0.2007406169185788</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.05399033860117941</v>
+        <v>-0.4556709296773129</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.06211675020189908</v>
+        <v>-0.1809809179378997</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
         <v>-0</v>
@@ -4524,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.05753555440308916</v>
+        <v>0.357332246623919</v>
       </c>
       <c r="AM8" t="n">
         <v>-0</v>
@@ -4533,13 +4533,13 @@
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.06692468641435227</v>
+        <v>0.1105079278586931</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.1510550103319466</v>
+        <v>-0.1858024631792063</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
         <v>-0</v>
@@ -4548,22 +4548,22 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.4012210113325229</v>
+        <v>1.716530802866336</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.01306373595801226</v>
+        <v>-0.2711362897776961</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.5503145890794698</v>
+        <v>-0.6107013642164573</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -4572,13 +4572,13 @@
         <v>-0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.1735334416913395</v>
+        <v>-0.5819687448278155</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,10 +4587,10 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.1067608278672856</v>
+        <v>-0.2689609360229874</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.1680232339083514</v>
+        <v>0.02049538622569079</v>
       </c>
       <c r="BI8" t="n">
         <v>-0</v>
@@ -4602,10 +4602,10 @@
         <v>-0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.1556789339865939</v>
+        <v>0.1356244800788722</v>
       </c>
       <c r="BN8" t="n">
         <v>-0</v>
@@ -4614,40 +4614,40 @@
         <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>-0.0146194061496221</v>
+        <v>0.1856584314732913</v>
       </c>
       <c r="BQ8" t="n">
-        <v>-0.05649260644983728</v>
+        <v>0.138081535516047</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
         <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.2012630801908264</v>
+        <v>0.6717759998778456</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.0133257623008405</v>
+        <v>-0.2066270931128476</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.2780819243863177</v>
+        <v>-0.3640407200538752</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB8" t="n">
         <v>-0</v>
@@ -4656,25 +4656,25 @@
         <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.1223278527839813</v>
+        <v>-0.3235804982403826</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.005254409864869247</v>
+        <v>0.1642646099514525</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.1166734183213457</v>
+        <v>0.2099296872523417</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
@@ -4686,88 +4686,88 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.03203105746107171</v>
+        <v>-0.3656273692701761</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.05774787397121428</v>
+        <v>0.3987913114132937</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.03359273767830079</v>
+        <v>0.1828538613029201</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
         <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.1011671876862124</v>
+        <v>-0.2866392965304727</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.02000480567697621</v>
+        <v>0.1642145868638853</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.1152215963757141</v>
+        <v>0.2822667615579754</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
         <v>-0</v>
       </c>
       <c r="DD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.1182314721727722</v>
+        <v>-0.2345592387079171</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0926421827238085</v>
+        <v>-0.3778626267774362</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.2106009833430011</v>
+        <v>0.2633023963166696</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
       </c>
       <c r="DL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.0650262641083721</v>
+        <v>0.09170580695657705</v>
       </c>
       <c r="DP8" t="n">
         <v>0</v>
@@ -4776,79 +4776,79 @@
         <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01764735801618293</v>
+        <v>-0.1085135878109885</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.09823997440730246</v>
+        <v>0.1877288249857243</v>
       </c>
       <c r="DT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW8" t="n">
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.06208792487795206</v>
+        <v>-0.2975882033812618</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.05390000122820674</v>
+        <v>0.06958224986686548</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.1122000894311024</v>
+        <v>0.05441078486052926</v>
       </c>
       <c r="EC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.07026254395707772</v>
+        <v>-0.2004448273991978</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.03001384433022367</v>
+        <v>0.116022166178487</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.003749114743894364</v>
+        <v>-0.06518256046486244</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.04986972815706415</v>
+        <v>0.1983197487913107</v>
       </c>
       <c r="EQ8" t="n">
         <v>0</v>
@@ -4857,52 +4857,52 @@
         <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.04334645757282828</v>
+        <v>0.006200669851622103</v>
       </c>
       <c r="ET8" t="n">
-        <v>-0.05738573424440058</v>
+        <v>0.1785873061320501</v>
       </c>
       <c r="EU8" t="n">
         <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
         <v>0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.1014138461645648</v>
+        <v>-0.3596955428639713</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
         <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.003386850940089787</v>
+        <v>0.09376687730621741</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.1088160320204838</v>
+        <v>0.2474087535909296</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.03453703976720383</v>
+        <v>-0.2007603589976811</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
@@ -4911,13 +4911,13 @@
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.03300842387970353</v>
+        <v>0.1265693348354134</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.1145182047420687</v>
+        <v>0.2646402280863294</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
         <v>0</v>
@@ -4929,19 +4929,19 @@
         <v>0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.0108966448489025</v>
+        <v>-0.1418217932065887</v>
       </c>
       <c r="FR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS8" t="n">
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.140430721209814</v>
+        <v>0.3975011866316001</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.1777522919048</v>
+        <v>-0.1703091867510553</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
@@ -4953,28 +4953,28 @@
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.04727438391383657</v>
+        <v>-0.01817749321557701</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.1039745515608788</v>
+        <v>0.07345275855659406</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
         <v>0</v>
@@ -4985,43 +4985,43 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3815591499003186</v>
+        <v>0.4461305712729974</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.04031820273067106</v>
+        <v>-0.1986620095522671</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1372862478133693</v>
+        <v>0.01181099634678071</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2435578500743352</v>
+        <v>0.4504705668989015</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.05174992223808234</v>
+        <v>-0.2690757329511134</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1157256571373122</v>
+        <v>-0.05319611388135223</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5039,79 +5039,79 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.07085902158143438</v>
+        <v>0.07390396228625766</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.008882736592941261</v>
+        <v>-0.05825248555488427</v>
       </c>
       <c r="W9" t="n">
-        <v>0.04507021695259513</v>
+        <v>-0.01881476674452279</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.03407889997012099</v>
+        <v>0.009764027054499792</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.01273148610218255</v>
+        <v>-0.1502414545083642</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.01709980036681078</v>
+        <v>0.01144924257941493</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001000983457054746</v>
+        <v>0.1088075246020502</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.04944051060127548</v>
+        <v>-0.06124552354016068</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.06932520049972174</v>
+        <v>0.09845015623371056</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
@@ -5120,25 +5120,25 @@
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.2604126056039317</v>
+        <v>0.3047941533022991</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.05322798495097165</v>
+        <v>-0.07950848856990177</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.03162657731251656</v>
+        <v>-0.1318852038334846</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
         <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
         <v>-0</v>
@@ -5147,25 +5147,25 @@
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.02234415291684705</v>
+        <v>-0.005861337058742435</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.08897726345042128</v>
+        <v>-0.1051546304923273</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1265616280370284</v>
+        <v>-0.01611512253239625</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,16 +5174,16 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.09905711066796725</v>
+        <v>-0.003149744362867394</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.03361156205481524</v>
+        <v>0.004925217054181013</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1060862496961958</v>
+        <v>0.04210998662296928</v>
       </c>
       <c r="BQ9" t="n">
         <v>-0</v>
@@ -5198,100 +5198,100 @@
         <v>-0</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.1318263427938593</v>
+        <v>0.2154682670337422</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.02683384308305879</v>
+        <v>-0.04338195055731589</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.02556803323831543</v>
+        <v>-0.02500136902072409</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.06842268743063633</v>
+        <v>-0.1247219495712694</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>-0.007370990906041244</v>
+        <v>0.09834728440461291</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.00174222058358812</v>
+        <v>-0.0133724601163946</v>
       </c>
       <c r="CI9" t="n">
         <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.001543126283749217</v>
+        <v>-0.1024331777876969</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.03297968427095651</v>
+        <v>0.1382949193181361</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.08622357198756364</v>
+        <v>0.03873126281042349</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
         <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.04864314265208998</v>
+        <v>-0.1213552857570784</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.008126848658402783</v>
+        <v>0.1107492481003431</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.005188538148519289</v>
+        <v>-0.005546055592276195</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
@@ -5309,16 +5309,16 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.06851578783708522</v>
+        <v>-0.07312814168706695</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.05839160801293795</v>
+        <v>0.04822040261229554</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.03828391387821059</v>
+        <v>-0.0445480601830337</v>
       </c>
       <c r="DJ9" t="n">
         <v>-0</v>
@@ -5333,22 +5333,22 @@
         <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.03758317981213508</v>
+        <v>-0.07336638472573317</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.06052461104964519</v>
+        <v>-0.0612509612091002</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.03833446326475788</v>
+        <v>-0.002849066979302629</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
@@ -5363,52 +5363,52 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.05442476172407507</v>
+        <v>-0.1008983247691735</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.01820028796003152</v>
+        <v>0.04576855740015798</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.03268597666039669</v>
+        <v>0.0363914610438491</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
         <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.07101584452534648</v>
+        <v>-0.1048014177554082</v>
       </c>
       <c r="EH9" t="n">
         <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.003949653990835863</v>
+        <v>0.09924609789597735</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.06245577001313934</v>
+        <v>0.007229874952478376</v>
       </c>
       <c r="EK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
@@ -5417,22 +5417,22 @@
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.001217797657538762</v>
+        <v>0.02896946540527011</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.003610769204830474</v>
+        <v>0.04087595639908014</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.03441009876344996</v>
+        <v>0.00506994986952817</v>
       </c>
       <c r="ET9" t="n">
         <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,16 +5444,16 @@
         <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.05125216831541067</v>
+        <v>-0.1394693185391009</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>-0.004213261535751177</v>
+        <v>0.1195182165512341</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.009170404765505871</v>
+        <v>-0.01989906592662548</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
@@ -5465,49 +5465,49 @@
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.007312756378878193</v>
+        <v>-0.03327846927940543</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.02002750736334317</v>
+        <v>0.06910947984829478</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.05103089366939924</v>
+        <v>-0.1128259980178284</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
       </c>
       <c r="FM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.04224751003496299</v>
+        <v>-0.1750365850483613</v>
       </c>
       <c r="FR9" t="n">
         <v>-0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.06318730042829301</v>
+        <v>0.06186546127645406</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.01581456421084561</v>
+        <v>0.1411185388781749</v>
       </c>
       <c r="FU9" t="n">
         <v>-0</v>
@@ -5516,34 +5516,34 @@
         <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX9" t="n">
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.01914538716685472</v>
+        <v>-0.1072203876966592</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.04661998742545439</v>
+        <v>0.06450276871826796</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>-0</v>
